--- a/F3M_Controlling_assessment_ready_AI_v0.xlsx
+++ b/F3M_Controlling_assessment_ready_AI_v0.xlsx
@@ -136,7 +136,7 @@
     <t>Modelo de fast/continuous close con checklist inteligente, alertas de dependencias y automatización del seguimiento de tareas.</t>
   </si>
   <si>
-    <t>Automated closing checklists; touchless close; proactive defect resolution recommendations</t>
+    <t>Listas de verificación de cierre automatizadas; cierre sin intervención; recomendaciones proactivas para la resolución de incidencias</t>
   </si>
   <si>
     <t>¿Existe un calendario formal de cierre?
@@ -172,7 +172,7 @@
     <t>Identificación predictiva de accruals esperados, detección de omisiones y propuestas de asiento/ajuste con workflow de aprobación.</t>
   </si>
   <si>
-    <t>Identify missing monthly accruals; Journal Entry Automation &amp; Close Value prediction; suspect journal entry monitoring</t>
+    <t>Identificación de provisiones mensuales omitidas; Automatización de asientos contables y predicción del valor de cierre; monitorización de asientos sospechosos</t>
   </si>
   <si>
     <t>¿Qué asientos son manuales vs automáticos?
@@ -205,10 +205,10 @@
     <t>Controles automatizados, con alertas, umbrales y priorización de revisiones por materialidad/riesgo.</t>
   </si>
   <si>
-    <t>Detección AI de asientos inusuales o sospechosos durante el cierre, con scoring de anomalía, explicación y workflow de investigación.</t>
-  </si>
-  <si>
-    <t>Identify unusual entries during close period; monitor suspect journal entries in real time</t>
+    <t>Detección IA de asientos inusuales o sospechosos durante el cierre, con scoring de anomalía, explicación y workflow de investigación.</t>
+  </si>
+  <si>
+    <t>Identificación de asientos inusuales durante el periodo de cierre; monitorización en tiempo real de asientos sospechosos</t>
   </si>
   <si>
     <t>¿Existen controles preventivos?
@@ -241,10 +241,10 @@
     <t>Análisis causa-raíz de retrasos, acciones de mejora, reducción de reprocesos y automatización progresiva.</t>
   </si>
   <si>
-    <t>Cierre basado en process mining y AI para detectar cuellos de botella, excepciones recurrentes y oportunidades de touchless close.</t>
-  </si>
-  <si>
-    <t>Capture variations and exceptions in P2P/O2C enabling touchless close; AI-enabled process mining</t>
+    <t>Cierre basado en process mining y IA para detectar cuellos de botella, excepciones recurrentes y oportunidades de touchless close.</t>
+  </si>
+  <si>
+    <t>Captura de variaciones y excepciones en P2P/O2C que habilita el cierre sin intervención; Minería de procesos con IA</t>
   </si>
   <si>
     <t>¿Se mide la duración del cierre?
@@ -283,7 +283,7 @@
     <t>Modelo de consolidación inteligente capaz de detectar inconsistencias de estructura, cambios de perímetro y riesgos de calidad de dato.</t>
   </si>
   <si>
-    <t>Identify inconsistencies in master data records; guided workflows for master data record changes</t>
+    <t>Identificación de inconsistencias en los registros de datos maestros; flujos guiados para cambios en datos maestros</t>
   </si>
   <si>
     <t>¿Existe perímetro formal?
@@ -316,10 +316,10 @@
     <t>Reglas automatizadas, trazables y controladas, con validaciones y gestión de excepciones.</t>
   </si>
   <si>
-    <t>Automatización avanzada de consolidación multiestándar/multimoneda, con recomendaciones sobre ajustes, validación AI y alertas de inconsistencia.</t>
-  </si>
-  <si>
-    <t>Consolidate accounting records under different standards and currencies</t>
+    <t>Automatización avanzada de consolidación multiestándar/multimoneda, con recomendaciones sobre ajustes, validación IA y alertas de inconsistencia.</t>
+  </si>
+  <si>
+    <t>Consolidación de registros contables bajo distintas normas y divisas</t>
   </si>
   <si>
     <t>¿Las reglas están documentadas?
@@ -352,10 +352,10 @@
     <t>Integración automatizada con validaciones, reconciliaciones y gestión estructurada de incidencias.</t>
   </si>
   <si>
-    <t>Automatización de datos financieros multifuente y detección AI de inconsistencias en datos maestros/financieros antes de consolidar.</t>
-  </si>
-  <si>
-    <t>Automate financial data across diverse sources; identify inconsistencies in master data records</t>
+    <t>Automatización de datos financieros multifuente y detección IA de inconsistencias en datos maestros/financieros antes de consolidar.</t>
+  </si>
+  <si>
+    <t>Automatización de datos financieros de fuentes diversas; identificación de inconsistencias en los registros de datos maestros</t>
   </si>
   <si>
     <t>¿Las cargas son automáticas?
@@ -391,7 +391,7 @@
     <t>Generación automática de informes consolidados, narratives y explicaciones de variaciones con GenAI, con revisión humana y controles de compliance.</t>
   </si>
   <si>
-    <t>Consolidate written financial reports; generate account variance analysis and intelligent explanations</t>
+    <t>Consolidación de informes financieros redactados; generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿El reporting consolidado llega a tiempo?
@@ -430,7 +430,7 @@
     <t>Automated financial statement preparation con generación asistida de notas/secciones y validaciones de consistencia antes de revisión.</t>
   </si>
   <si>
-    <t>Automated financial statement preparation</t>
+    <t>Preparación automatizada de estados financieros</t>
   </si>
   <si>
     <t>¿Se preparan estados desde fuente única?
@@ -466,7 +466,7 @@
     <t>Generación GenAI de borradores de regulatory filings con interpretación normativa, trazabilidad y human review.</t>
   </si>
   <si>
-    <t>Generate draft regulatory filings; draft sections of 10Q/10K; financial rules and regulations interpretations</t>
+    <t>Generación de borradores de informes regulatorios; borradores de secciones de 10Q/10K; interpretación de normas y regulación financiera</t>
   </si>
   <si>
     <t>¿Existe calendario regulatorio?
@@ -502,7 +502,7 @@
     <t>Generación de borrador de informes financieros por medio de GenAI, manteniendo evidencia, controles de consistencia de la información, habilitando al mismo tiempo la revisión humana y el control de cambios.</t>
   </si>
   <si>
-    <t>Narrative MD&amp;A draft generation; consolidate written financial reports into one compliant report</t>
+    <t>Generación del borrador narrativo del MD&amp;A; consolidación de informes financieros en un único informe conforme a normativa</t>
   </si>
   <si>
     <t>¿La narrativa está soportada por datos?
@@ -535,10 +535,10 @@
     <t>Controles integrados con workflow, trazabilidad de cambios, revisión y gestión de incidencias.</t>
   </si>
   <si>
-    <t>Modelo AI-enabled de revisión de consistencia, detección de anomalías en cifras/narrativas y alertas de compliance en reporting externo.</t>
-  </si>
-  <si>
-    <t>Financial rules interpretations; automated report consolidation; anomaly detection during close</t>
+    <t>Modelo basado en IA de revisión de consistencia, detección de anomalías en cifras/narrativas y alertas de compliance en reporting externo.</t>
+  </si>
+  <si>
+    <t>Interpretación de normas financieras; consolidación automatizada de informes; detección de anomalías durante el cierre</t>
   </si>
   <si>
     <t>¿Existe matriz de control?
@@ -577,7 +577,7 @@
     <t>Generación automática de account variance analysis e intelligent explanations con GenAI, incluyendo drivers, causas y narrativa ejecutiva.</t>
   </si>
   <si>
-    <t>Generate account variance analysis and intelligent explanations</t>
+    <t>Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿Existe metodología de variance analysis?
@@ -610,10 +610,10 @@
     <t>Validaciones automatizadas, gobierno de datos maestros y gestión estructurada de incidencias.</t>
   </si>
   <si>
-    <t>Detección AI de inconsistencias en master data, errores de clasificación de gastos y documentación automática de metadata.</t>
-  </si>
-  <si>
-    <t>Identify inconsistencies in master data; identify expense classification errors; generate metadata documentation</t>
+    <t>Detección IA de inconsistencias en master data, errores de clasificación de gastos y documentación automática de metadata.</t>
+  </si>
+  <si>
+    <t>Identificación de inconsistencias en los datos maestros; identificación de errores de clasificación de gastos; generación de documentación de metadatos</t>
   </si>
   <si>
     <t>¿Hay reglas de calidad de dato?
@@ -649,7 +649,7 @@
     <t>Digital analyst / FinanceAI Insights Platform con análisis bajo demanda, investigación y primeras conclusiones desde múltiples fuentes.</t>
   </si>
   <si>
-    <t>FinanceAI Insights Platform; Digital Analyst on demand analytics</t>
+    <t>FinanceAI Insights Platform; Analítica bajo demanda con Digital Analyst</t>
   </si>
   <si>
     <t>¿El análisis genera insights?
@@ -682,10 +682,10 @@
     <t>Modelos predictivos recurrentes para anticipar desviaciones y oportunidades.</t>
   </si>
   <si>
-    <t>AI identifica patrones históricos para predecir performance futura, detectar desviaciones tempranas y recomendar acciones.</t>
-  </si>
-  <si>
-    <t>Identify past data patterns to predict and improve future financial performance</t>
+    <t>IA identifica patrones históricos para predecir performance futura, detectar desviaciones tempranas y recomendar acciones.</t>
+  </si>
+  <si>
+    <t>Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Se anticipan desviaciones?
@@ -724,7 +724,7 @@
     <t>Reporting interno con generación automática de commentary, insights y narrative reporting desde múltiples fuentes financieras.</t>
   </si>
   <si>
-    <t>Mgmt reporting actuals/plan/variance + commentary; automate financial data across diverse sources</t>
+    <t>informes de gestión con real/plan/desviación y comentario; automatización de datos financieros de fuentes diversas</t>
   </si>
   <si>
     <t>¿Existe catálogo de informes?
@@ -757,10 +757,10 @@
     <t>Single source of truth con integración automática, modelo semántico y control de calidad.</t>
   </si>
   <si>
-    <t>Capa AI/automation para integrar datos financieros de fuentes diversas, detectar inconsistencias y habilitar reporting autoservicio.</t>
-  </si>
-  <si>
-    <t>Automate financial data across diverse sources; identify inconsistencies in master data</t>
+    <t>Capa IA/automation para integrar datos financieros de fuentes diversas, detectar inconsistencias y habilitar reporting autoservicio.</t>
+  </si>
+  <si>
+    <t>Automatización de datos financieros de fuentes diversas; identificación de inconsistencias en los datos maestros</t>
   </si>
   <si>
     <t>¿Existe fuente oficial?
@@ -796,7 +796,7 @@
     <t>Chat-with-my-Finance-data / Digital Analyst para consultas en lenguaje natural, insights y explicación automática de resultados.</t>
   </si>
   <si>
-    <t>Chat with Finance data; FinanceAI Insights Platform</t>
+    <t>Conversación con los datos de Finanzas; FinanceAI Insights Platform</t>
   </si>
   <si>
     <t>¿Existe autoservicio?
@@ -829,10 +829,10 @@
     <t>Reporting conectado con acciones, owners, beneficios esperados y seguimiento.</t>
   </si>
   <si>
-    <t>AI genera recomendaciones de acciones, identifica riesgos/oportunidades y prepara packs ejecutivos con decisiones sugeridas.</t>
-  </si>
-  <si>
-    <t>Digital analyst; project-level recommendations; executive financial health overview</t>
+    <t>IA genera recomendaciones de acciones, identifica riesgos/oportunidades y prepara packs ejecutivos con decisiones sugeridas.</t>
+  </si>
+  <si>
+    <t>Digital analyst; recomendaciones a nivel de proyecto; visión ejecutiva de la salud financiera</t>
   </si>
   <si>
     <t>¿Hay comités de revisión?
@@ -868,10 +868,10 @@
     <t>Proceso integrado en el cierre, con seguimiento de incidencias, escalados y KPIs.</t>
   </si>
   <si>
-    <t>Conciliación intercompany integrada con alertas tempranas, workflow y priorización AI de partidas críticas.</t>
-  </si>
-  <si>
-    <t>AI-enabled reconciliation; automated closing checklists</t>
+    <t>Conciliación intercompany integrada con alertas tempranas, workflow y priorización IA de partidas críticas.</t>
+  </si>
+  <si>
+    <t>Conciliación con IA; listas de verificación de cierre automatizadas</t>
   </si>
   <si>
     <t>¿Existe calendario?
@@ -904,10 +904,10 @@
     <t>Matching automatizado con reglas avanzadas, workflow de resolución y análisis causa-raíz.</t>
   </si>
   <si>
-    <t>AI/NLP reconciliation a nivel transacción contra documentos soporte, con matching inteligente, explicación de diferencias y recomendaciones de resolución.</t>
-  </si>
-  <si>
-    <t>Reconcile account balances at transaction level to invoices, purchase orders and bank statements</t>
+    <t>IA/NLP reconciliation a nivel transacción contra documentos soporte, con matching inteligente, explicación de diferencias y recomendaciones de resolución.</t>
+  </si>
+  <si>
+    <t>Conciliación de saldos contables a nivel de transacción con facturas, pedidos de compra y extractos bancarios</t>
   </si>
   <si>
     <t>¿Qué porcentaje se matchea automáticamente?
@@ -940,10 +940,10 @@
     <t>Acciones preventivas, reglas de eliminación, acuerdos intercompany y mejora continua.</t>
   </si>
   <si>
-    <t>Modelos AI detectan patrones de diferencias recurrentes, predicen riesgos de desbalance y recomiendan cambios preventivos.</t>
-  </si>
-  <si>
-    <t>Predictive compliance monitoring; identify unusual entries during close</t>
+    <t>Modelos IA detectan patrones de diferencias recurrentes, predicen riesgos de desbalance y recomiendan cambios preventivos.</t>
+  </si>
+  <si>
+    <t>Monitorización predictiva del cumplimiento; identificación de asientos inusuales durante el cierre</t>
   </si>
   <si>
     <t>¿Se identifican causas recurrentes?
@@ -976,10 +976,10 @@
     <t>Integración automática con consolidación, eliminaciones, reporting y seguimiento de impactos.</t>
   </si>
   <si>
-    <t>Conciliación IC automatizada conectada con consolidación multiestándar/multimoneda y detección AI de impactos en reporting.</t>
-  </si>
-  <si>
-    <t>Consolidate accounting records under different standards and currencies; AI reconciliation</t>
+    <t>Conciliación IC automatizada conectada con consolidación multiestándar/multimoneda y detección IA de impactos en reporting.</t>
+  </si>
+  <si>
+    <t>Consolidación de registros contables bajo distintas normas y divisas; Conciliación con IA</t>
   </si>
   <si>
     <t>¿La conciliación alimenta consolidación?

--- a/F3M_Controlling_assessment_ready_AI_v0.xlsx
+++ b/F3M_Controlling_assessment_ready_AI_v0.xlsx
@@ -1045,7 +1045,7 @@
     <t>Generación GenAI de borradores de regulatory filings / secciones 10Q-10K con interpretación normativa, trazabilidad y human review.</t>
   </si>
   <si>
-    <t>3.3 Narrative reporting y MD&amp;A</t>
+    <t>3.3 Narrative reporting y envío ESEF</t>
   </si>
   <si>
     <t>Narrative MD&amp;A draft generation y consolidation of written reports con GenAI, manteniendo evidencia, consistencia y revisión humana.</t>

--- a/F3M_Controlling_assessment_ready_AI_v0.xlsx
+++ b/F3M_Controlling_assessment_ready_AI_v0.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="371">
   <si>
     <t>Capacidad</t>
   </si>
@@ -1148,6 +1148,93 @@
   </si>
   <si>
     <t>Assessment, Resumen, Heatmap, Roadmap, AI Overlay, Guias scoring e Instrucciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist inteligente de cierre; Cierre sin intervención sobre P2P y O2C; Recomendaciones de resolución de incidencias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de provisiones omitidas; Automatización de asientos y previsión del cierre; Vigilancia en tiempo real de asientos sospechosos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de asientos inusuales en el cierre; Vigilancia en tiempo real de asientos sospechosos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cierre sin intervención sobre P2P y O2C; Minería de procesos del cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de inconsistencias en datos maestros; Flujos guiados de cambio en datos maestros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidación multinorma y multidivisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integración automatizada de datos financieros; Detección de inconsistencias en datos maestros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidación de informes en un único documento; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación asistida de estados financieros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrador de informes regulatorios; Borrador de secciones 10Q y 10K; Interpretación de normativa financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrador narrativo del MD&amp;A; Consolidación de informes en un único documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretación de normativa financiera; Consolidación de informes en un único documento; Detección de asientos inusuales en el cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de inconsistencias en datos maestros; Detección de errores de clasificación de gasto; Generación de documentación de metadatos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informes de gestión con comentario automático; Integración automatizada de datos financieros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista digital de Finanzas bajo demanda; Recomendaciones de acción a nivel de proyecto; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conciliación a nivel de transacción; Checklist inteligente de cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conciliación a nivel de transacción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitorización predictiva del cumplimiento; Detección de asientos inusuales en el cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidación multinorma y multidivisa; Conciliación a nivel de transacción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consolidación multinorma y multidivisa; Detección de inconsistencias en datos maestros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación asistida de estados financieros; Consolidación de informes en un único documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis de desviaciones con explicación automática; Informes de gestión con comentario automático</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista digital de Finanzas bajo demanda; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrones históricos para predecir el rendimiento; Previsión y escenarios bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista digital de Finanzas bajo demanda; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conciliación a nivel de transacción; Recomendaciones de resolución de incidencias</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +1995,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>342</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1966,7 +2053,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>343</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -2024,7 +2111,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>344</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -2082,7 +2169,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>345</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -2140,7 +2227,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>346</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2198,7 +2285,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>364</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -2256,7 +2343,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2314,7 +2401,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>349</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2372,7 +2459,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>365</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2430,7 +2517,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>351</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2488,7 +2575,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>352</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2546,7 +2633,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>353</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2604,7 +2691,7 @@
         <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>163</v>
+        <v>366</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2662,7 +2749,7 @@
         <v>173</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>174</v>
+        <v>355</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2720,7 +2807,7 @@
         <v>184</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>185</v>
+        <v>367</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2778,7 +2865,7 @@
         <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>196</v>
+        <v>368</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2836,7 +2923,7 @@
         <v>207</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>208</v>
+        <v>358</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -2894,7 +2981,7 @@
         <v>218</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2952,7 +3039,7 @@
         <v>229</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -3010,7 +3097,7 @@
         <v>240</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>241</v>
+        <v>359</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -3068,7 +3155,7 @@
         <v>252</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>253</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -3126,7 +3213,7 @@
         <v>263</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>264</v>
+        <v>370</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -3184,7 +3271,7 @@
         <v>274</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -3242,7 +3329,7 @@
         <v>285</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>286</v>
+        <v>363</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4735,7 +4822,7 @@
       </c>
       <c r="F2" s="2" t="str">
         <f>Assessment!I2</f>
-        <v>Automated closing checklists; touchless close; proactive defect resolution recommendations</v>
+        <v/>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G25" si="0">IF(D2="Alta","Oleada 1",IF(D2="Media","Oleada 2","Oleada 3"))</f>
@@ -4770,7 +4857,7 @@
       </c>
       <c r="F3" s="2" t="str">
         <f>Assessment!I3</f>
-        <v>Identify missing monthly accruals; Journal Entry Automation &amp; Close Value prediction; suspect journal entry monitoring</v>
+        <v/>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4805,7 +4892,7 @@
       </c>
       <c r="F4" s="2" t="str">
         <f>Assessment!I4</f>
-        <v>Identify unusual entries during close period; monitor suspect journal entries in real time</v>
+        <v/>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4840,7 +4927,7 @@
       </c>
       <c r="F5" s="2" t="str">
         <f>Assessment!I5</f>
-        <v>Capture variations and exceptions in P2P/O2C enabling touchless close; AI-enabled process mining</v>
+        <v/>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4875,7 +4962,7 @@
       </c>
       <c r="F6" s="2" t="str">
         <f>Assessment!I6</f>
-        <v>Identify inconsistencies in master data records; guided workflows for master data record changes</v>
+        <v/>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4910,7 +4997,7 @@
       </c>
       <c r="F7" s="2" t="str">
         <f>Assessment!I7</f>
-        <v>Consolidate accounting records under different standards and currencies</v>
+        <v/>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4945,7 +5032,7 @@
       </c>
       <c r="F8" s="2" t="str">
         <f>Assessment!I8</f>
-        <v>Automate financial data across diverse sources; identify inconsistencies in master data records</v>
+        <v/>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4980,7 +5067,7 @@
       </c>
       <c r="F9" s="2" t="str">
         <f>Assessment!I9</f>
-        <v>Consolidate written financial reports; generate account variance analysis and intelligent explanations</v>
+        <v/>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5015,7 +5102,7 @@
       </c>
       <c r="F10" s="2" t="str">
         <f>Assessment!I10</f>
-        <v>Automated financial statement preparation</v>
+        <v/>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5050,7 +5137,7 @@
       </c>
       <c r="F11" s="2" t="str">
         <f>Assessment!I11</f>
-        <v>Generate draft regulatory filings; draft sections of 10Q/10K; financial rules and regulations interpretations</v>
+        <v/>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5085,7 +5172,7 @@
       </c>
       <c r="F12" s="2" t="str">
         <f>Assessment!I12</f>
-        <v>Narrative MD&amp;A draft generation; consolidate written financial reports into one compliant report</v>
+        <v/>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5120,7 +5207,7 @@
       </c>
       <c r="F13" s="2" t="str">
         <f>Assessment!I13</f>
-        <v>Financial rules interpretations; automated report consolidation; anomaly detection during close</v>
+        <v/>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5155,7 +5242,7 @@
       </c>
       <c r="F14" s="2" t="str">
         <f>Assessment!I14</f>
-        <v>Generate account variance analysis and intelligent explanations</v>
+        <v/>
       </c>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5190,7 +5277,7 @@
       </c>
       <c r="F15" s="2" t="str">
         <f>Assessment!I15</f>
-        <v>Identify inconsistencies in master data; identify expense classification errors; generate metadata documentation</v>
+        <v/>
       </c>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5225,7 +5312,7 @@
       </c>
       <c r="F16" s="2" t="str">
         <f>Assessment!I16</f>
-        <v>FinanceAI Insights Platform; Digital Analyst on demand analytics</v>
+        <v/>
       </c>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5260,7 +5347,7 @@
       </c>
       <c r="F17" s="2" t="str">
         <f>Assessment!I17</f>
-        <v>Identify past data patterns to predict and improve future financial performance</v>
+        <v/>
       </c>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5295,7 +5382,7 @@
       </c>
       <c r="F18" s="2" t="str">
         <f>Assessment!I18</f>
-        <v>Mgmt reporting actuals/plan/variance + commentary; automate financial data across diverse sources</v>
+        <v/>
       </c>
       <c r="G18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5330,7 +5417,7 @@
       </c>
       <c r="F19" s="2" t="str">
         <f>Assessment!I19</f>
-        <v>Automate financial data across diverse sources; identify inconsistencies in master data</v>
+        <v/>
       </c>
       <c r="G19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5365,7 +5452,7 @@
       </c>
       <c r="F20" s="2" t="str">
         <f>Assessment!I20</f>
-        <v>Chat with Finance data; FinanceAI Insights Platform</v>
+        <v/>
       </c>
       <c r="G20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5400,7 +5487,7 @@
       </c>
       <c r="F21" s="2" t="str">
         <f>Assessment!I21</f>
-        <v>Digital analyst; project-level recommendations; executive financial health overview</v>
+        <v/>
       </c>
       <c r="G21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5435,7 +5522,7 @@
       </c>
       <c r="F22" s="2" t="str">
         <f>Assessment!I22</f>
-        <v>AI-enabled reconciliation; automated closing checklists</v>
+        <v/>
       </c>
       <c r="G22" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5470,7 +5557,7 @@
       </c>
       <c r="F23" s="2" t="str">
         <f>Assessment!I23</f>
-        <v>Reconcile account balances at transaction level to invoices, purchase orders and bank statements</v>
+        <v/>
       </c>
       <c r="G23" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5505,7 +5592,7 @@
       </c>
       <c r="F24" s="2" t="str">
         <f>Assessment!I24</f>
-        <v>Predictive compliance monitoring; identify unusual entries during close</v>
+        <v/>
       </c>
       <c r="G24" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5540,7 +5627,7 @@
       </c>
       <c r="F25" s="2" t="str">
         <f>Assessment!I25</f>
-        <v>Consolidate accounting records under different standards and currencies; AI reconciliation</v>
+        <v/>
       </c>
       <c r="G25" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5600,7 +5687,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>342</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -5617,7 +5704,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>343</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -5634,7 +5721,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>344</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -5651,7 +5738,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>345</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -5668,7 +5755,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>346</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -5685,7 +5772,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>364</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -5702,7 +5789,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -5719,7 +5806,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>349</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -5736,7 +5823,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>365</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -5753,7 +5840,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>351</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>306</v>
@@ -5770,7 +5857,7 @@
         <v>307</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>352</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>308</v>
@@ -5787,7 +5874,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>353</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>
@@ -5804,7 +5891,7 @@
         <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>366</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>162</v>
@@ -5821,7 +5908,7 @@
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>174</v>
+        <v>355</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>173</v>
@@ -5838,7 +5925,7 @@
         <v>178</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>185</v>
+        <v>367</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>184</v>
@@ -5855,7 +5942,7 @@
         <v>189</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>196</v>
+        <v>368</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>195</v>
@@ -5872,7 +5959,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>208</v>
+        <v>358</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>207</v>
@@ -5889,7 +5976,7 @@
         <v>212</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>218</v>
@@ -5906,7 +5993,7 @@
         <v>223</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>229</v>
@@ -5923,7 +6010,7 @@
         <v>234</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>359</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>240</v>
@@ -5940,7 +6027,7 @@
         <v>246</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>253</v>
+        <v>360</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>252</v>
@@ -5957,7 +6044,7 @@
         <v>257</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>264</v>
+        <v>370</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>263</v>
@@ -5974,7 +6061,7 @@
         <v>268</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>274</v>
@@ -5991,7 +6078,7 @@
         <v>279</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>286</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>285</v>

--- a/F3M_Controlling_assessment_ready_AI_v0.xlsx
+++ b/F3M_Controlling_assessment_ready_AI_v0.xlsx
@@ -133,7 +133,7 @@
     <t>Cierre integrado, medido por KPIs, con dependencias controladas y mejora continua de plazos/calidad.</t>
   </si>
   <si>
-    <t>Modelo de fast/continuous close con checklist inteligente, alertas de dependencias y automatización del seguimiento de tareas.</t>
+    <t>Modelo de cierre rápido y continuo con checklist inteligente, alertas de dependencias y automatización del seguimiento de tareas.</t>
   </si>
   <si>
     <t>Listas de verificación de cierre automatizadas; cierre sin intervención; recomendaciones proactivas para la resolución de incidencias</t>
@@ -169,7 +169,7 @@
     <t>Automatización integrada de asientos recurrentes, accruals y validaciones, con trazabilidad y control de excepciones.</t>
   </si>
   <si>
-    <t>Identificación predictiva de accruals esperados, detección de omisiones y propuestas de asiento/ajuste con workflow de aprobación.</t>
+    <t>Identificación predictiva de devengos esperados, detección de omisiones y propuestas de asiento/ajuste con circuito de aprobación.</t>
   </si>
   <si>
     <t>Identificación de provisiones mensuales omitidas; Automatización de asientos contables y predicción del valor de cierre; monitorización de asientos sospechosos</t>
@@ -205,7 +205,7 @@
     <t>Controles automatizados, con alertas, umbrales y priorización de revisiones por materialidad/riesgo.</t>
   </si>
   <si>
-    <t>Detección IA de asientos inusuales o sospechosos durante el cierre, con scoring de anomalía, explicación y workflow de investigación.</t>
+    <t>Detección IA de asientos inusuales o sospechosos durante el cierre, con puntuación de anomalía, explicación y flujo de trabajo de investigación.</t>
   </si>
   <si>
     <t>Identificación de asientos inusuales durante el periodo de cierre; monitorización en tiempo real de asientos sospechosos</t>
@@ -241,7 +241,7 @@
     <t>Análisis causa-raíz de retrasos, acciones de mejora, reducción de reprocesos y automatización progresiva.</t>
   </si>
   <si>
-    <t>Cierre basado en process mining y IA para detectar cuellos de botella, excepciones recurrentes y oportunidades de touchless close.</t>
+    <t>Cierre basado en minería de procesos y IA para detectar cuellos de botella, excepciones recurrentes y oportunidades de cierre sin intervención.</t>
   </si>
   <si>
     <t>Captura de variaciones y excepciones en P2P/O2C que habilita el cierre sin intervención; Minería de procesos con IA</t>
@@ -388,7 +388,7 @@
     <t>Reporting automatizado con análisis de variaciones, explicaciones, revisiones y controles de consistencia.</t>
   </si>
   <si>
-    <t>Generación automática de informes consolidados, narratives y explicaciones de variaciones con GenAI, con revisión humana y controles de compliance.</t>
+    <t>Generación automática de informes consolidados, narrativas y explicaciones de variaciones con GenAI, con revisión humana y controles de cumplimiento.</t>
   </si>
   <si>
     <t>Consolidación de informes financieros redactados; generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
@@ -427,7 +427,7 @@
     <t>Preparación integrada y automatizada con trazabilidad desde dato origen y controles de consistencia.</t>
   </si>
   <si>
-    <t>Automated financial statement preparation con generación asistida de notas/secciones y validaciones de consistencia antes de revisión.</t>
+    <t>Preparación automatizada de los estados financieros, con generación asistida de notas y secciones y validación de consistencia antes de la revisión.</t>
   </si>
   <si>
     <t>Preparación automatizada de estados financieros</t>
@@ -463,7 +463,7 @@
     <t>Proceso integrado con datos financieros y regulatorios, controles automáticos y gestión de cambios normativos.</t>
   </si>
   <si>
-    <t>Generación GenAI de borradores de regulatory filings con interpretación normativa, trazabilidad y human review.</t>
+    <t>Generación GenAI de borradores de informes regulatorios con interpretación normativa, trazabilidad y revisión humana.</t>
   </si>
   <si>
     <t>Generación de borradores de informes regulatorios; borradores de secciones de 10Q/10K; interpretación de normas y regulación financiera</t>
@@ -535,7 +535,7 @@
     <t>Controles integrados con workflow, trazabilidad de cambios, revisión y gestión de incidencias.</t>
   </si>
   <si>
-    <t>Modelo basado en IA de revisión de consistencia, detección de anomalías en cifras/narrativas y alertas de compliance en reporting externo.</t>
+    <t>Modelo basado en IA de revisión de consistencia, detección de anomalías en cifras/narrativas y alertas de cumplimiento en los informes externos.</t>
   </si>
   <si>
     <t>Interpretación de normas financieras; consolidación automatizada de informes; detección de anomalías durante el cierre</t>
@@ -574,7 +574,7 @@
     <t>Análisis integrado con datos, drivers, acciones y conexión con reporting/forecast.</t>
   </si>
   <si>
-    <t>Generación automática de account variance analysis e intelligent explanations con GenAI, incluyendo drivers, causas y narrativa ejecutiva.</t>
+    <t>Generación automática del análisis de desviaciones por cuenta y de su explicación con GenAI, incluyendo drivers, causas y narrativa ejecutiva.</t>
   </si>
   <si>
     <t>Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
@@ -610,7 +610,7 @@
     <t>Validaciones automatizadas, gobierno de datos maestros y gestión estructurada de incidencias.</t>
   </si>
   <si>
-    <t>Detección IA de inconsistencias en master data, errores de clasificación de gastos y documentación automática de metadata.</t>
+    <t>Detección IA de inconsistencias en datos maestros, errores de clasificación de gastos y documentación automática de metadatos.</t>
   </si>
   <si>
     <t>Identificación de inconsistencias en los datos maestros; identificación de errores de clasificación de gastos; generación de documentación de metadatos</t>
@@ -646,7 +646,7 @@
     <t>Insights recurrentes, priorizados y conectados con decisiones, acciones y forecast.</t>
   </si>
   <si>
-    <t>Digital analyst / FinanceAI Insights Platform con análisis bajo demanda, investigación y primeras conclusiones desde múltiples fuentes.</t>
+    <t>Analista digital sobre la plataforma FinanceAI Insights Platform, con análisis bajo demanda, investigación y primeras conclusiones a partir de múltiples fuentes.</t>
   </si>
   <si>
     <t>FinanceAI Insights Platform; Analítica bajo demanda con Digital Analyst</t>
@@ -682,7 +682,7 @@
     <t>Modelos predictivos recurrentes para anticipar desviaciones y oportunidades.</t>
   </si>
   <si>
-    <t>IA identifica patrones históricos para predecir performance futura, detectar desviaciones tempranas y recomendar acciones.</t>
+    <t>La IA identifica patrones históricos para predecir el rendimiento futuro, detectar desviaciones tempranas y recomendar acciones.</t>
   </si>
   <si>
     <t>Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
@@ -721,7 +721,7 @@
     <t>Reporting integrado, automatizado y con drill-down, análisis de variaciones y acciones.</t>
   </si>
   <si>
-    <t>Reporting interno con generación automática de commentary, insights y narrative reporting desde múltiples fuentes financieras.</t>
+    <t>Informes internos con generación automática del comentario, de las conclusiones y de la narrativa, a partir de múltiples fuentes financieras.</t>
   </si>
   <si>
     <t>informes de gestión con real/plan/desviación y comentario; automatización de datos financieros de fuentes diversas</t>
@@ -757,7 +757,7 @@
     <t>Single source of truth con integración automática, modelo semántico y control de calidad.</t>
   </si>
   <si>
-    <t>Capa IA/automation para integrar datos financieros de fuentes diversas, detectar inconsistencias y habilitar reporting autoservicio.</t>
+    <t>Capa de IA y automatización para integrar datos financieros de fuentes diversas, detectar inconsistencias y habilitar los informes en autoservicio.</t>
   </si>
   <si>
     <t>Automatización de datos financieros de fuentes diversas; identificación de inconsistencias en los datos maestros</t>
@@ -793,7 +793,7 @@
     <t>Autoservicio gobernado con drill-down, narrativa, flujos de aprobación y control de acceso.</t>
   </si>
   <si>
-    <t>Chat-with-my-Finance-data / Digital Analyst para consultas en lenguaje natural, insights y explicación automática de resultados.</t>
+    <t>Consulta conversacional de los datos de Finanzas con el analista digital, para preguntar en lenguaje natural y obtener la explicación automática de los resultados.</t>
   </si>
   <si>
     <t>Conversación con los datos de Finanzas; FinanceAI Insights Platform</t>
@@ -829,7 +829,7 @@
     <t>Reporting conectado con acciones, owners, beneficios esperados y seguimiento.</t>
   </si>
   <si>
-    <t>IA genera recomendaciones de acciones, identifica riesgos/oportunidades y prepara packs ejecutivos con decisiones sugeridas.</t>
+    <t>IA genera recomendaciones de acciones, identifica riesgos/oportunidades y prepara informes ejecutivos con decisiones sugeridas.</t>
   </si>
   <si>
     <t>Digital analyst; recomendaciones a nivel de proyecto; visión ejecutiva de la salud financiera</t>
@@ -868,7 +868,7 @@
     <t>Proceso integrado en el cierre, con seguimiento de incidencias, escalados y KPIs.</t>
   </si>
   <si>
-    <t>Conciliación intercompany integrada con alertas tempranas, workflow y priorización IA de partidas críticas.</t>
+    <t>Conciliación intercompany integrada con alertas tempranas, flujo de trabajo y priorización IA de partidas críticas.</t>
   </si>
   <si>
     <t>Conciliación con IA; listas de verificación de cierre automatizadas</t>
@@ -904,7 +904,7 @@
     <t>Matching automatizado con reglas avanzadas, workflow de resolución y análisis causa-raíz.</t>
   </si>
   <si>
-    <t>IA/NLP reconciliation a nivel transacción contra documentos soporte, con matching inteligente, explicación de diferencias y recomendaciones de resolución.</t>
+    <t>Conciliación con IA y NLP a nivel de transacción contra los documentos soporte, con emparejamiento inteligente, explicación de las diferencias y recomendación de resolución.</t>
   </si>
   <si>
     <t>Conciliación de saldos contables a nivel de transacción con facturas, pedidos de compra y extractos bancarios</t>
@@ -976,7 +976,7 @@
     <t>Integración automática con consolidación, eliminaciones, reporting y seguimiento de impactos.</t>
   </si>
   <si>
-    <t>Conciliación IC automatizada conectada con consolidación multiestándar/multimoneda y detección IA de impactos en reporting.</t>
+    <t>Conciliación intercompany automatizada, conectada con la consolidación multiestándar y multidivisa, y detección con IA de su impacto en los informes.</t>
   </si>
   <si>
     <t>Consolidación de registros contables bajo distintas normas y divisas; Conciliación con IA</t>
@@ -1042,7 +1042,7 @@
     <t>FinanceAI - Use Cases Summary_C / F3M AI Use Case Mapping</t>
   </si>
   <si>
-    <t>Generación GenAI de borradores de regulatory filings / secciones 10Q-10K con interpretación normativa, trazabilidad y human review.</t>
+    <t>Generación con GenAI de borradores de informes regulatorios y de secciones 10Q y 10K, con interpretación normativa, trazabilidad de la fuente y revisión humana.</t>
   </si>
   <si>
     <t>3.3 Narrative reporting y envío ESEF</t>

--- a/F3M_Controlling_assessment_ready_AI_v0.xlsx
+++ b/F3M_Controlling_assessment_ready_AI_v0.xlsx
@@ -148,7 +148,7 @@
     <t>Calendario de cierre; RACI; checklist; actas de cierre; KPIs de días de cierre; evidencias de aprobaciones.</t>
   </si>
   <si>
-    <t>Implantar gobierno de cierre con calendario, RACI, checklist digital, KPIs y tracking de dependencias.</t>
+    <t>Implantar gobierno de cierre con calendario, RACI, lista de verificación digital, KPIs y seguimiento de dependencias.</t>
   </si>
   <si>
     <t>1.2 Automatización de asientos, accruals y ajustes</t>
@@ -184,7 +184,7 @@
     <t>Listado de asientos recurrentes; plantillas de accruals; logs de automatización; conciliación de ajustes; workflow de aprobación.</t>
   </si>
   <si>
-    <t>Crear modelo de automatización de asientos y accruals con reglas, históricos, validaciones y alertas de omisión.</t>
+    <t>Crear modelo de automatización de asientos y periodificaciones con reglas, históricos, validaciones y alertas de omisión.</t>
   </si>
   <si>
     <t>1.3 Control de calidad y anomalías del cierre</t>
@@ -220,7 +220,7 @@
     <t>Matriz de controles; logs de excepción; evidencias de revisión; reportes de anomalías; auditoría de cambios.</t>
   </si>
   <si>
-    <t>Implantar monitor de anomalías de cierre con reglas, modelos de detección, scoring y workflow de revisión.</t>
+    <t>Implantar monitor de anomalías de cierre con reglas, modelos de detección, puntuación de riesgo y flujo de revisión.</t>
   </si>
   <si>
     <t>1.4 Eficiencia, coordinación y mejora continua del cierre</t>
@@ -256,7 +256,7 @@
     <t>KPIs de cierre; backlog de incidencias; planes de mejora; análisis causa-raíz; métricas de retrabajo.</t>
   </si>
   <si>
-    <t>Crear programa de mejora continua del cierre con KPIs, process mining, análisis de excepciones y roadmap de automatización.</t>
+    <t>Crear programa de mejora continua del cierre con KPIs, minería de procesos, análisis de excepciones y hoja de ruta de automatización.</t>
   </si>
   <si>
     <t>Consolidación</t>
@@ -295,7 +295,7 @@
     <t>Perímetro; jerarquías; manual de consolidación; logs de cambios; matriz de ownership.</t>
   </si>
   <si>
-    <t>Formalizar gobierno de perímetro y jerarquías con workflow de cambios, validaciones y trazabilidad.</t>
+    <t>Formalizar gobierno de perímetro y jerarquías con flujo de cambios, validaciones y trazabilidad.</t>
   </si>
   <si>
     <t>2.2 Eliminaciones, ajustes y reglas de consolidación</t>
@@ -403,7 +403,7 @@
     <t>Pack de reporting; estados consolidados; análisis de variaciones; actas de revisión; evidencias de control.</t>
   </si>
   <si>
-    <t>Desarrollar reporting consolidado automatizado con narrative commentary, explicación de variaciones y control de consistencia.</t>
+    <t>Desarrollar informes consolidados automatizados con comentario narrativo, explicación de variaciones y control de consistencia.</t>
   </si>
   <si>
     <t>Informes externos</t>
@@ -478,7 +478,7 @@
     <t>Calendario regulatorio; filings; matriz de requisitos; evidencias de revisión; control de fuentes.</t>
   </si>
   <si>
-    <t>Implantar workflow de filings regulatorios con generación asistida, validaciones, trazabilidad y tracking de cambios normativos.</t>
+    <t>Implantar flujo de presentaciones a reguladores con generación asistida, validaciones, trazabilidad y seguimiento de cambios normativos.</t>
   </si>
   <si>
     <t>3.3 Narrative reporting y envío ESEF</t>
@@ -550,7 +550,7 @@
     <t>Matriz de control; evidencias; auditoría de cambios; checklists; incidencias; aprobaciones.</t>
   </si>
   <si>
-    <t>Implantar governance digital de reporting externo con evidencias, workflow de revisión y detección de inconsistencias.</t>
+    <t>Implantar gobierno digital de la información externa con evidencias, flujo de revisión y detección de inconsistencias.</t>
   </si>
   <si>
     <t>Análisis financiero</t>
@@ -589,7 +589,7 @@
     <t>Reportes de variaciones; árboles de drivers; comentarios; actas; acciones; dashboards.</t>
   </si>
   <si>
-    <t>Crear modelo estándar de variance analysis con drivers, explicaciones, owners y acciones.</t>
+    <t>Crear modelo estándar de análisis de desviaciones con drivers, explicaciones, responsables y acciones.</t>
   </si>
   <si>
     <t>4.2 Calidad, clasificación y consistencia de datos financieros</t>
@@ -625,7 +625,7 @@
     <t>Catálogo de datos; reglas de calidad; incidencias; maestros; documentación de metadata; logs de corrección.</t>
   </si>
   <si>
-    <t>Implementar control de calidad y clasificación financiera con detección de anomalías, metadata y workflows de remediación.</t>
+    <t>Implementar control de calidad y clasificación financiera con detección de anomalías, metadatos y flujos de corrección.</t>
   </si>
   <si>
     <t>4.3 Insight financiero y explicación de performance</t>
@@ -661,7 +661,7 @@
     <t>Packs ejecutivos; dashboards; one-pagers; recomendaciones; comités de performance; decisiones documentadas.</t>
   </si>
   <si>
-    <t>Desarrollar capa de insights financieros con narrativa, drivers, recomendaciones y conexión con decisiones.</t>
+    <t>Desarrollar capa de análisis financiero con narrativa, drivers, recomendaciones y conexión con decisiones.</t>
   </si>
   <si>
     <t>4.4 Análisis predictivo y detección temprana</t>
@@ -697,7 +697,7 @@
     <t>Modelos predictivos; dashboards de alertas; backtesting; supuestos; acciones derivadas.</t>
   </si>
   <si>
-    <t>Implantar modelos predictivos de performance, desviaciones y oportunidades con alertas y recomendaciones.</t>
+    <t>Implantar modelos predictivos de rendimiento, desviaciones y oportunidades con alertas y recomendaciones.</t>
   </si>
   <si>
     <t>Informes internos</t>
@@ -736,7 +736,7 @@
     <t>Catálogo de reporting; KPIs; dashboards; periodicidad; owners; evidencias de automatización.</t>
   </si>
   <si>
-    <t>Rediseñar reporting interno con KPIs homologados, automatización, narrative commentary y drill-down.</t>
+    <t>Rediseñar los informes internos con KPIs homologados, automatización, comentario narrativo y navegación al detalle.</t>
   </si>
   <si>
     <t>5.2 Integración de datos y single source of truth</t>
@@ -772,7 +772,7 @@
     <t>Modelo de datos; fuentes oficiales; logs de carga; definición de KPIs; validaciones; controles de calidad.</t>
   </si>
   <si>
-    <t>Implantar capa de datos financieros para reporting interno con integración, calidad y gobierno de definiciones.</t>
+    <t>Implantar capa de datos financieros para informes internos con integración, calidad y gobierno de definiciones.</t>
   </si>
   <si>
     <t>5.3 Narrativa de gestión y autoservicio</t>
@@ -808,7 +808,7 @@
     <t>Dashboards; permisos; modelo semántico; guías de uso; logs de consulta; feedback de usuarios.</t>
   </si>
   <si>
-    <t>Habilitar self-service financiero gobernado con capa conversacional, narrativa y trazabilidad de definiciones.</t>
+    <t>Habilitar autoservicio financiero gobernado con capa conversacional, narrativa y trazabilidad de definiciones.</t>
   </si>
   <si>
     <t>5.4 Rutinas de revisión y acciones de gestión</t>
@@ -844,7 +844,7 @@
     <t>Actas; trackers de acciones; KPIs de impacto; packs de reporting; decisiones documentadas.</t>
   </si>
   <si>
-    <t>Formalizar rutinas de reporting interno con decisiones, acciones, owners, seguimiento e insights automatizados.</t>
+    <t>Formalizar rutinas de informes internos con decisiones, acciones, responsables, seguimiento y conclusiones automatizadas.</t>
   </si>
   <si>
     <t>Conciliación intercompany</t>
@@ -883,7 +883,7 @@
     <t>Calendario; RACI; reportes IC; KPIs; actas de escalado; evidencias.</t>
   </si>
   <si>
-    <t>Diseñar gobierno de conciliación IC con calendario, umbrales, workflow y seguimiento de partidas abiertas.</t>
+    <t>Diseñar gobierno de conciliación intercompañía con calendario, umbrales, flujo de trabajo y seguimiento de partidas abiertas.</t>
   </si>
   <si>
     <t>6.2 Matching, diferencias y resolución de partidas</t>
@@ -919,7 +919,7 @@
     <t>Reportes de matching; partidas abiertas; logs de excepción; workflow de resolución; análisis causa-raíz.</t>
   </si>
   <si>
-    <t>Implantar matching inteligente y workflow de resolución IC con análisis causa-raíz y priorización por materialidad.</t>
+    <t>Implantar casación inteligente y flujo de resolución intercompañía con análisis causa-raíz y priorización por materialidad.</t>
   </si>
   <si>
     <t>6.3 Prevención y reducción de diferencias recurrentes</t>
@@ -955,7 +955,7 @@
     <t>Análisis de recurrencia; planes de acción; acuerdos IC; reglas de eliminación; KPIs de aging.</t>
   </si>
   <si>
-    <t>Crear programa de reducción de diferencias IC con análisis de patrones, acciones preventivas y seguimiento de aging.</t>
+    <t>Crear programa de reducción de diferencias intercompañía con análisis de patrones, acciones preventivas y seguimiento de antigüedad.</t>
   </si>
   <si>
     <t>6.4 Integración con consolidación y reporting</t>
@@ -991,7 +991,7 @@
     <t>Reportes IC; consolidación; eliminaciones; ajustes; logs de integración; KPIs de late adjustments.</t>
   </si>
   <si>
-    <t>Integrar conciliación IC con consolidación, eliminaciones, reporting y alertas de impacto antes del cierre.</t>
+    <t>Integrar conciliación intercompañía con consolidación, eliminaciones, informes y alertas de impacto antes del cierre.</t>
   </si>
   <si>
     <t>Score global dominio</t>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E2" s="2" t="str">
         <f>Assessment!S2</f>
-        <v>Implantar gobierno de cierre con calendario, RACI, checklist digital, KPIs y tracking de dependencias.</v>
+        <v>Implantar gobierno de cierre con calendario, RACI, lista de verificación digital, KPIs y seguimiento de dependencias.</v>
       </c>
       <c r="F2" s="2" t="str">
         <f>Assessment!I2</f>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E3" s="2" t="str">
         <f>Assessment!S3</f>
-        <v>Crear modelo de automatización de asientos y accruals con reglas, históricos, validaciones y alertas de omisión.</v>
+        <v>Crear modelo de automatización de asientos y periodificaciones con reglas, históricos, validaciones y alertas de omisión.</v>
       </c>
       <c r="F3" s="2" t="str">
         <f>Assessment!I3</f>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="E4" s="2" t="str">
         <f>Assessment!S4</f>
-        <v>Implantar monitor de anomalías de cierre con reglas, modelos de detección, scoring y workflow de revisión.</v>
+        <v>Implantar monitor de anomalías de cierre con reglas, modelos de detección, puntuación de riesgo y flujo de revisión.</v>
       </c>
       <c r="F4" s="2" t="str">
         <f>Assessment!I4</f>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="E5" s="2" t="str">
         <f>Assessment!S5</f>
-        <v>Crear programa de mejora continua del cierre con KPIs, process mining, análisis de excepciones y roadmap de automatización.</v>
+        <v>Crear programa de mejora continua del cierre con KPIs, minería de procesos, análisis de excepciones y hoja de ruta de automatización.</v>
       </c>
       <c r="F5" s="2" t="str">
         <f>Assessment!I5</f>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="E6" s="2" t="str">
         <f>Assessment!S6</f>
-        <v>Formalizar gobierno de perímetro y jerarquías con workflow de cambios, validaciones y trazabilidad.</v>
+        <v>Formalizar gobierno de perímetro y jerarquías con flujo de cambios, validaciones y trazabilidad.</v>
       </c>
       <c r="F6" s="2" t="str">
         <f>Assessment!I6</f>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="E9" s="2" t="str">
         <f>Assessment!S9</f>
-        <v>Desarrollar reporting consolidado automatizado con narrative commentary, explicación de variaciones y control de consistencia.</v>
+        <v>Desarrollar informes consolidados automatizados con comentario narrativo, explicación de variaciones y control de consistencia.</v>
       </c>
       <c r="F9" s="2" t="str">
         <f>Assessment!I9</f>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E11" s="2" t="str">
         <f>Assessment!S11</f>
-        <v>Implantar workflow de filings regulatorios con generación asistida, validaciones, trazabilidad y tracking de cambios normativos.</v>
+        <v>Implantar flujo de presentaciones a reguladores con generación asistida, validaciones, trazabilidad y seguimiento de cambios normativos.</v>
       </c>
       <c r="F11" s="2" t="str">
         <f>Assessment!I11</f>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E13" s="2" t="str">
         <f>Assessment!S13</f>
-        <v>Implantar governance digital de reporting externo con evidencias, workflow de revisión y detección de inconsistencias.</v>
+        <v>Implantar gobierno digital de la información externa con evidencias, flujo de revisión y detección de inconsistencias.</v>
       </c>
       <c r="F13" s="2" t="str">
         <f>Assessment!I13</f>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="E14" s="2" t="str">
         <f>Assessment!S14</f>
-        <v>Crear modelo estándar de variance analysis con drivers, explicaciones, owners y acciones.</v>
+        <v>Crear modelo estándar de análisis de desviaciones con drivers, explicaciones, responsables y acciones.</v>
       </c>
       <c r="F14" s="2" t="str">
         <f>Assessment!I14</f>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="E15" s="2" t="str">
         <f>Assessment!S15</f>
-        <v>Implementar control de calidad y clasificación financiera con detección de anomalías, metadata y workflows de remediación.</v>
+        <v>Implementar control de calidad y clasificación financiera con detección de anomalías, metadatos y flujos de corrección.</v>
       </c>
       <c r="F15" s="2" t="str">
         <f>Assessment!I15</f>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E16" s="2" t="str">
         <f>Assessment!S16</f>
-        <v>Desarrollar capa de insights financieros con narrativa, drivers, recomendaciones y conexión con decisiones.</v>
+        <v>Desarrollar capa de análisis financiero con narrativa, drivers, recomendaciones y conexión con decisiones.</v>
       </c>
       <c r="F16" s="2" t="str">
         <f>Assessment!I16</f>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="E17" s="2" t="str">
         <f>Assessment!S17</f>
-        <v>Implantar modelos predictivos de performance, desviaciones y oportunidades con alertas y recomendaciones.</v>
+        <v>Implantar modelos predictivos de rendimiento, desviaciones y oportunidades con alertas y recomendaciones.</v>
       </c>
       <c r="F17" s="2" t="str">
         <f>Assessment!I17</f>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="E18" s="2" t="str">
         <f>Assessment!S18</f>
-        <v>Rediseñar reporting interno con KPIs homologados, automatización, narrative commentary y drill-down.</v>
+        <v>Rediseñar los informes internos con KPIs homologados, automatización, comentario narrativo y navegación al detalle.</v>
       </c>
       <c r="F18" s="2" t="str">
         <f>Assessment!I18</f>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E19" s="2" t="str">
         <f>Assessment!S19</f>
-        <v>Implantar capa de datos financieros para reporting interno con integración, calidad y gobierno de definiciones.</v>
+        <v>Implantar capa de datos financieros para informes internos con integración, calidad y gobierno de definiciones.</v>
       </c>
       <c r="F19" s="2" t="str">
         <f>Assessment!I19</f>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E20" s="2" t="str">
         <f>Assessment!S20</f>
-        <v>Habilitar self-service financiero gobernado con capa conversacional, narrativa y trazabilidad de definiciones.</v>
+        <v>Habilitar autoservicio financiero gobernado con capa conversacional, narrativa y trazabilidad de definiciones.</v>
       </c>
       <c r="F20" s="2" t="str">
         <f>Assessment!I20</f>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E21" s="2" t="str">
         <f>Assessment!S21</f>
-        <v>Formalizar rutinas de reporting interno con decisiones, acciones, owners, seguimiento e insights automatizados.</v>
+        <v>Formalizar rutinas de informes internos con decisiones, acciones, responsables, seguimiento y conclusiones automatizadas.</v>
       </c>
       <c r="F21" s="2" t="str">
         <f>Assessment!I21</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E22" s="2" t="str">
         <f>Assessment!S22</f>
-        <v>Diseñar gobierno de conciliación IC con calendario, umbrales, workflow y seguimiento de partidas abiertas.</v>
+        <v>Diseñar gobierno de conciliación intercompañía con calendario, umbrales, flujo de trabajo y seguimiento de partidas abiertas.</v>
       </c>
       <c r="F22" s="2" t="str">
         <f>Assessment!I22</f>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="E23" s="2" t="str">
         <f>Assessment!S23</f>
-        <v>Implantar matching inteligente y workflow de resolución IC con análisis causa-raíz y priorización por materialidad.</v>
+        <v>Implantar casación inteligente y flujo de resolución intercompañía con análisis causa-raíz y priorización por materialidad.</v>
       </c>
       <c r="F23" s="2" t="str">
         <f>Assessment!I23</f>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E24" s="2" t="str">
         <f>Assessment!S24</f>
-        <v>Crear programa de reducción de diferencias IC con análisis de patrones, acciones preventivas y seguimiento de aging.</v>
+        <v>Crear programa de reducción de diferencias intercompañía con análisis de patrones, acciones preventivas y seguimiento de antigüedad.</v>
       </c>
       <c r="F24" s="2" t="str">
         <f>Assessment!I24</f>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="E25" s="2" t="str">
         <f>Assessment!S25</f>
-        <v>Integrar conciliación IC con consolidación, eliminaciones, reporting y alertas de impacto antes del cierre.</v>
+        <v>Integrar conciliación intercompañía con consolidación, eliminaciones, informes y alertas de impacto antes del cierre.</v>
       </c>
       <c r="F25" s="2" t="str">
         <f>Assessment!I25</f>
